--- a/fanta/Classifica_SarkiaLega-25-26.xlsx
+++ b/fanta/Classifica_SarkiaLega-25-26.xlsx
@@ -68,10 +68,10 @@
     <t>Score Edge FC</t>
   </si>
   <si>
+    <t>Perder Brema FC</t>
+  </si>
+  <si>
     <t>FC Schalke 104</t>
-  </si>
-  <si>
-    <t>Perder Brema FC</t>
   </si>
   <si>
     <t>Dura Lex</t>
@@ -269,7 +269,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5" s="6">
         <v>15</v>
@@ -278,22 +278,22 @@
         <v>6</v>
       </c>
       <c r="G5" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H5" s="6">
         <v>58</v>
       </c>
       <c r="I5" s="6">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J5" s="6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K5" s="7">
         <v>51</v>
       </c>
       <c r="L5" s="8">
-        <v>2235.5</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="6">
@@ -307,10 +307,10 @@
         <v>4</v>
       </c>
       <c r="D6" s="6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E6" s="6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6" s="6">
         <v>9</v>
@@ -319,19 +319,19 @@
         <v>9</v>
       </c>
       <c r="H6" s="6">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I6" s="6">
         <v>48</v>
       </c>
       <c r="J6" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K6" s="7">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L6" s="8">
-        <v>2223</v>
+        <v>2294.5</v>
       </c>
     </row>
     <row r="7">
@@ -345,31 +345,31 @@
         <v>4</v>
       </c>
       <c r="D7" s="6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7" s="6">
         <v>11</v>
       </c>
       <c r="F7" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7" s="6">
         <v>11</v>
       </c>
       <c r="H7" s="6">
+        <v>56</v>
+      </c>
+      <c r="I7" s="6">
         <v>54</v>
-      </c>
-      <c r="I7" s="6">
-        <v>52</v>
       </c>
       <c r="J7" s="6">
         <v>2</v>
       </c>
       <c r="K7" s="7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L7" s="8">
-        <v>2203</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="8">
@@ -383,13 +383,13 @@
         <v>4</v>
       </c>
       <c r="D8" s="6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E8" s="6">
         <v>11</v>
       </c>
       <c r="F8" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G8" s="6">
         <v>12</v>
@@ -404,10 +404,10 @@
         <v>-8</v>
       </c>
       <c r="K8" s="7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L8" s="8">
-        <v>2129</v>
+        <v>2192.5</v>
       </c>
     </row>
     <row r="9">
@@ -421,31 +421,31 @@
         <v>4</v>
       </c>
       <c r="D9" s="6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E9" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" s="6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G9" s="6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H9" s="6">
         <v>46</v>
       </c>
       <c r="I9" s="6">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="J9" s="6">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="K9" s="7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L9" s="8">
-        <v>2158.5</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="10">
@@ -459,31 +459,31 @@
         <v>4</v>
       </c>
       <c r="D10" s="6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E10" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F10" s="6">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G10" s="6">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H10" s="6">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I10" s="6">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J10" s="6">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="K10" s="7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L10" s="8">
-        <v>2147.5</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="11">
@@ -497,31 +497,31 @@
         <v>4</v>
       </c>
       <c r="D11" s="6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E11" s="6">
         <v>9</v>
       </c>
       <c r="F11" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G11" s="6">
         <v>12</v>
       </c>
       <c r="H11" s="6">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I11" s="6">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J11" s="6">
         <v>-6</v>
       </c>
       <c r="K11" s="7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L11" s="8">
-        <v>2131</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="12">
@@ -535,31 +535,31 @@
         <v>4</v>
       </c>
       <c r="D12" s="6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E12" s="6">
         <v>10</v>
       </c>
       <c r="F12" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G12" s="6">
         <v>14</v>
       </c>
       <c r="H12" s="6">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I12" s="6">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J12" s="6">
         <v>-6</v>
       </c>
       <c r="K12" s="7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L12" s="8">
-        <v>2119.5</v>
+        <v>2192</v>
       </c>
     </row>
   </sheetData>

--- a/fanta/Classifica_SarkiaLega-25-26.xlsx
+++ b/fanta/Classifica_SarkiaLega-25-26.xlsx
@@ -407,7 +407,7 @@
         <v>41</v>
       </c>
       <c r="L8" s="8">
-        <v>2192.5</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="9">

--- a/fanta/Classifica_SarkiaLega-25-26.xlsx
+++ b/fanta/Classifica_SarkiaLega-25-26.xlsx
@@ -62,22 +62,22 @@
     <t>FC Kremoton</t>
   </si>
   <si>
+    <t>Score Edge FC</t>
+  </si>
+  <si>
+    <t>FC Schalke 104</t>
+  </si>
+  <si>
     <t>drunk boys</t>
   </si>
   <si>
-    <t>Score Edge FC</t>
-  </si>
-  <si>
     <t>Perder Brema FC</t>
   </si>
   <si>
-    <t>FC Schalke 104</t>
+    <t>Infadawork do Brasil</t>
   </si>
   <si>
     <t>Dura Lex</t>
-  </si>
-  <si>
-    <t>Infadawork do Brasil</t>
   </si>
 </sst>
 </file>
@@ -269,31 +269,31 @@
         <v>4</v>
       </c>
       <c r="D5" s="6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E5" s="6">
         <v>15</v>
       </c>
       <c r="F5" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G5" s="6">
         <v>10</v>
       </c>
       <c r="H5" s="6">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I5" s="6">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J5" s="6">
         <v>10</v>
       </c>
       <c r="K5" s="7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L5" s="8">
-        <v>2295</v>
+        <v>2366.5</v>
       </c>
     </row>
     <row r="6">
@@ -307,7 +307,7 @@
         <v>4</v>
       </c>
       <c r="D6" s="6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E6" s="6">
         <v>13</v>
@@ -316,22 +316,22 @@
         <v>9</v>
       </c>
       <c r="G6" s="6">
+        <v>10</v>
+      </c>
+      <c r="H6" s="6">
+        <v>60</v>
+      </c>
+      <c r="I6" s="6">
+        <v>51</v>
+      </c>
+      <c r="J6" s="6">
         <v>9</v>
-      </c>
-      <c r="H6" s="6">
-        <v>58</v>
-      </c>
-      <c r="I6" s="6">
-        <v>48</v>
-      </c>
-      <c r="J6" s="6">
-        <v>10</v>
       </c>
       <c r="K6" s="7">
         <v>48</v>
       </c>
       <c r="L6" s="8">
-        <v>2294.5</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="7">
@@ -345,31 +345,31 @@
         <v>4</v>
       </c>
       <c r="D7" s="6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7" s="6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F7" s="6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G7" s="6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H7" s="6">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="I7" s="6">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J7" s="6">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="K7" s="7">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L7" s="8">
-        <v>2275</v>
+        <v>2263.5</v>
       </c>
     </row>
     <row r="8">
@@ -383,31 +383,31 @@
         <v>4</v>
       </c>
       <c r="D8" s="6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8" s="6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F8" s="6">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G8" s="6">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H8" s="6">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I8" s="6">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="J8" s="6">
-        <v>-8</v>
+        <v>3</v>
       </c>
       <c r="K8" s="7">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L8" s="8">
-        <v>2193</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="9">
@@ -421,31 +421,31 @@
         <v>4</v>
       </c>
       <c r="D9" s="6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E9" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F9" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G9" s="6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H9" s="6">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="I9" s="6">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="J9" s="6">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="K9" s="7">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L9" s="8">
-        <v>2224</v>
+        <v>2340.5</v>
       </c>
     </row>
     <row r="10">
@@ -459,31 +459,31 @@
         <v>4</v>
       </c>
       <c r="D10" s="6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E10" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F10" s="6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G10" s="6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H10" s="6">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I10" s="6">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J10" s="6">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="K10" s="7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L10" s="8">
-        <v>2222</v>
+        <v>2290.5</v>
       </c>
     </row>
     <row r="11">
@@ -497,31 +497,31 @@
         <v>4</v>
       </c>
       <c r="D11" s="6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E11" s="6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F11" s="6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G11" s="6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H11" s="6">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I11" s="6">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J11" s="6">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="K11" s="7">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L11" s="8">
-        <v>2206</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="12">
@@ -535,31 +535,31 @@
         <v>4</v>
       </c>
       <c r="D12" s="6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E12" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F12" s="6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G12" s="6">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H12" s="6">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I12" s="6">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="J12" s="6">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="K12" s="7">
         <v>37</v>
       </c>
       <c r="L12" s="8">
-        <v>2192</v>
+        <v>2272</v>
       </c>
     </row>
   </sheetData>
